--- a/artfynd/A 29535-2025 artfynd.xlsx
+++ b/artfynd/A 29535-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135545544</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135545546</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135545549</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135545553</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,6 +1197,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135545545</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135545550</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1396,6 +1431,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135545551</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1508,6 +1548,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135545547</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1620,6 +1665,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135545552</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135545548</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1844,8 +1899,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135545554</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 29535-2025 artfynd.xlsx
+++ b/artfynd/A 29535-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135545544</v>
       </c>
       <c r="B2" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135545546</v>
       </c>
       <c r="B3" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135545549</v>
       </c>
       <c r="B4" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135545553</v>
       </c>
       <c r="B5" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135545545</v>
       </c>
       <c r="B6" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>135545550</v>
       </c>
       <c r="B7" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>135545551</v>
       </c>
       <c r="B8" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>135545547</v>
       </c>
       <c r="B9" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>135545552</v>
       </c>
       <c r="B10" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>135545548</v>
       </c>
       <c r="B11" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>135545554</v>
       </c>
       <c r="B12" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 29535-2025 artfynd.xlsx
+++ b/artfynd/A 29535-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135545544</v>
       </c>
       <c r="B2" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135545546</v>
       </c>
       <c r="B3" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135545549</v>
       </c>
       <c r="B4" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135545553</v>
       </c>
       <c r="B5" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135545545</v>
       </c>
       <c r="B6" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>135545550</v>
       </c>
       <c r="B7" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>135545551</v>
       </c>
       <c r="B8" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>135545547</v>
       </c>
       <c r="B9" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>135545552</v>
       </c>
       <c r="B10" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>135545548</v>
       </c>
       <c r="B11" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>135545554</v>
       </c>
       <c r="B12" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 29535-2025 artfynd.xlsx
+++ b/artfynd/A 29535-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135545544</v>
       </c>
       <c r="B2" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135545546</v>
       </c>
       <c r="B3" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135545549</v>
       </c>
       <c r="B4" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135545553</v>
       </c>
       <c r="B5" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29535-2025 artfynd.xlsx
+++ b/artfynd/A 29535-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135545544</v>
       </c>
       <c r="B2" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135545546</v>
       </c>
       <c r="B3" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135545549</v>
       </c>
       <c r="B4" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135545553</v>
       </c>
       <c r="B5" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135545545</v>
       </c>
       <c r="B6" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>135545550</v>
       </c>
       <c r="B7" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>135545551</v>
       </c>
       <c r="B8" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>135545547</v>
       </c>
       <c r="B9" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>135545552</v>
       </c>
       <c r="B10" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>135545548</v>
       </c>
       <c r="B11" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>135545554</v>
       </c>
       <c r="B12" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 29535-2025 artfynd.xlsx
+++ b/artfynd/A 29535-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135545544</v>
       </c>
       <c r="B2" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135545546</v>
       </c>
       <c r="B3" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135545549</v>
       </c>
       <c r="B4" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135545553</v>
       </c>
       <c r="B5" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135545545</v>
       </c>
       <c r="B6" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>135545550</v>
       </c>
       <c r="B7" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>135545551</v>
       </c>
       <c r="B8" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>135545547</v>
       </c>
       <c r="B9" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>135545552</v>
       </c>
       <c r="B10" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>135545548</v>
       </c>
       <c r="B11" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>135545554</v>
       </c>
       <c r="B12" t="n">
-        <v>79466</v>
+        <v>79467</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
